--- a/gpu-finetune-memory-sizing.xlsx
+++ b/gpu-finetune-memory-sizing.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -188,6 +188,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1045,7 +1048,7 @@
         </is>
       </c>
       <c r="B44" s="15">
-        <f>IF($B$29="On",$B$85,$B$84)/1000000000</f>
+        <f>IF($B$29="On",$B$86,$B$85)/1000000000</f>
         <v/>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1088,7 +1091,7 @@
         </is>
       </c>
       <c r="B47" s="15">
-        <f>$B$68+IF($B$29="On",$B$71,$B$70)</f>
+        <f>$B$69+IF($B$29="On",$B$71,$B$70)</f>
         <v/>
       </c>
     </row>
@@ -1344,7 +1347,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>LoRA A (d x r) + B (r x d) = 2rd per replaced weight. GQA K/V are approximated as full-width — error is &lt;10% and dwarfed by frozen base.</t>
+          <t>The formula uses 2rd per target for every LoRA projection. GQA-narrowed K/V are actually narrower (d x d*kv/heads) and MLP projections (gate, up, down) are wider (d x ff_intermediate). At TinyLlama shapes the net error is ~28% overcount for attention-only and ~20% undercount for attention + MLP -- both dwarfed by the frozen base (adapter params are &lt;1% of base parameters).</t>
         </is>
       </c>
       <c r="D66" s="18" t="n"/>
@@ -1353,8 +1356,15 @@
       <c r="G66" s="18" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="n"/>
-      <c r="B67" s="18" t="n"/>
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Total adapter parameters (n_adapter)</t>
+        </is>
+      </c>
+      <c r="B67" s="26">
+        <f>B64*B65*B66</f>
+        <v/>
+      </c>
       <c r="C67" s="18" t="n"/>
       <c r="D67" s="18" t="n"/>
       <c r="E67" s="18" t="n"/>
@@ -1404,7 +1414,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Measured 1.35-1.71 GB across 18 non-checkpointed rows in runs/finetune-20260817-v3-finetune/results_finetune.csv. Provisioned at 1.2 to match Article 1's allowance.</t>
+          <t>Measured 0.79-6.52 GB across 20 non-checkpointed rows in runs/finetune-20260817-v3-finetune/results_finetune.csv. Range is narrow (1.30-1.73 GB) for baseline-adjacent configs; small at upper-N placements and wide at large batch/sequence shapes. Provisioned at 1.2 GB matching Article 1.</t>
         </is>
       </c>
       <c r="D70" s="18" t="n"/>
@@ -2545,7 +2555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every prediction column is computed by benchmark/predictions_finetune.py; measured columns come from runs/finetune-20260817-v3-finetune/results_finetune.csv. All 21 non-OOM rows land within +/-10% of measured max_allocated; the two boundary OOM misses are reported honestly, following Article 1's precedent.</t>
+          <t>Every prediction column is computed by benchmark/predictions_finetune.py; measured columns come from runs/finetune-20260817-v3-finetune/results_finetune.csv. All 23 non-OOM rows land within +/-10% of measured max_allocated; the 2 boundary OOM misses are reported honestly, following Article 1's precedent.</t>
         </is>
       </c>
     </row>
@@ -6886,6 +6896,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -6942,7 +6953,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Non-checkpointed rows: within +/-1% typical. Checkpointed rows: +2.9% / +8.3% / +8.3% (measured minus predicted). Two boundary-configurations at the 79 GB cliff came in as OOM at ~82 GB reserved when the formula predicted ~78 GB — reported honestly rather than tuned away, matching Article 1's precedent (its worst miss was 11.6% on checkpointing).</t>
+          <t>Non-checkpointed rows: within +/-1% typical. Checkpointed rows: +2.9% / +8.3% / +8.3% (measured minus predicted). Two boundary configurations at the 79 GB cliff came in as OOM at ~82 GB reserved when the formula predicted ~78 GB -- reported honestly rather than tuned away, matching Article 1's precedent (its worst miss was 11.6% on checkpointing). All 23 non-OOM rows land within +/-10%.</t>
         </is>
       </c>
     </row>
